--- a/templates/site_invoice/template_2.xlsx
+++ b/templates/site_invoice/template_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>Field</t>
   </si>
@@ -23,6 +23,9 @@
     <t>Example</t>
   </si>
   <si>
+    <t>TAX INVOICE</t>
+  </si>
+  <si>
     <t>Invoice Number</t>
   </si>
   <si>
@@ -45,9 +48,6 @@
   </si>
   <si>
     <t>D5</t>
-  </si>
-  <si>
-    <t>TAX INVOICE</t>
   </si>
   <si>
     <t>VENKATESHA REALTY LLP</t>
@@ -194,7 +194,10 @@
     <t>Add : SGST @ 9 % Of Gross</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Amt In Word :- </t>
+    <t>Total Amt In Word :-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Total.  </t>
   </si>
   <si>
     <t>‘I/We hereby certify that my/our registration certificate under the Maharashtra Value Added Tax Act. 2002 is in force on the date on which the sale of the goods specified in this tax invoice is made by me/us and that the transaction of sale covered by this tax invoice has been effected by me/us and it shall be accounted for in the turDECer of sale while filling of return and the due if any payable on the sale has been paid’.</t>
@@ -204,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -247,6 +250,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="8.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -266,7 +275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border/>
     <border>
       <left style="thin">
@@ -411,11 +420,47 @@
         <color rgb="FF808080"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -500,8 +545,15 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -509,7 +561,7 @@
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -744,7 +796,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1007,17 +1059,19 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="39"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="37"/>
+      <c r="A24" s="40"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="38"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="6"/>
@@ -1061,8 +1115,8 @@
       <c r="H30" s="9"/>
     </row>
     <row r="31" ht="12.0" customHeight="1">
-      <c r="A31" s="39" t="s">
-        <v>59</v>
+      <c r="A31" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -2079,7 +2133,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="G7:G8"/>
@@ -2095,6 +2149,7 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:D30"/>
     <mergeCell ref="A31:D38"/>
     <mergeCell ref="A9:C9"/>
@@ -2107,7 +2162,8 @@
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="E24:H38"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F15:H15"/>
@@ -2115,7 +2171,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F19:H19"/>
-    <mergeCell ref="E24:H38"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.25" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.25"/>
@@ -2153,32 +2208,32 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
